--- a/artfynd/A 9565-2024 artfynd.xlsx
+++ b/artfynd/A 9565-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117980649</v>
+        <v>117980650</v>
       </c>
       <c r="B2" t="n">
         <v>79561</v>

--- a/artfynd/A 9565-2024 artfynd.xlsx
+++ b/artfynd/A 9565-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117980650</v>
+        <v>117980696</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>97755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980696</v>
+        <v>117980593</v>
       </c>
       <c r="B3" t="n">
-        <v>97753</v>
+        <v>79100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117980593</v>
+        <v>117980649</v>
       </c>
       <c r="B4" t="n">
-        <v>79098</v>
+        <v>79563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
